--- a/artfynd/A 45569-2022 artfynd.xlsx
+++ b/artfynd/A 45569-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45569-2022 artfynd.xlsx
+++ b/artfynd/A 45569-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>342686</v>
+        <v>342685</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581612.7358936376</v>
+        <v>581613</v>
       </c>
       <c r="R2" t="n">
-        <v>7302464.563345989</v>
+        <v>7302465</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2007-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>312605</v>
+        <v>1931241</v>
       </c>
       <c r="B3" t="n">
-        <v>89387</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mårkadakmyran, Jill-Tsåtse, Ly lm</t>
+          <t>Jille-Tsåtse, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582074.4432203532</v>
+        <v>581789</v>
       </c>
       <c r="R3" t="n">
-        <v>7302026.577252668</v>
+        <v>7302633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,21 +855,11 @@
           <t>2007-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-09-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,12 +871,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>i gammal fjällnära granskog</t>
+          <t>i rasmark nedanför sydbranten i fjällnära läge</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>på granstubbe</t>
+          <t>på små marknära block</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -921,6 +891,434 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2705877</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jille-Tsåtse, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>581676</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7302596</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2007-09-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2007-09-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>i rasmark nedanför sydbranten i fjällnära läge</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>ganska stort bestånd på marken</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6538322</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jille-Tsåtse, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>581789</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7302633</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2007-09-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2007-09-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>i rasmark nedanför sydbranten i fjällnära läge</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>på små marknära block</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6429999</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jille-Tsåtse, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>581789</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7302633</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2007-09-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2007-09-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>i rasmark nedanför sydbranten i fjällnära läge</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>på små marknära block</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>312605</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91905</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mårkadakmyran, Jill-Tsåtse, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>582074</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7302027</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2007-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2007-09-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>i gammal fjällnära granskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45569-2022 artfynd.xlsx
+++ b/artfynd/A 45569-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/342685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1931241</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2705877</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6538322</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6429999</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,8 +1349,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/312605</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>